--- a/data/gold/results/scenarios/health_only/table_1.xlsx
+++ b/data/gold/results/scenarios/health_only/table_1.xlsx
@@ -415,19 +415,19 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>4405.157648990035</v>
+        <v>4119.043228087125</v>
       </c>
       <c r="C2">
-        <v>5123.295820701995</v>
+        <v>3684.859392415446</v>
       </c>
       <c r="D2">
-        <v>38.90477499646222</v>
+        <v>84.42245303168855</v>
       </c>
       <c r="E2">
-        <v>3414.079538858508</v>
+        <v>4097.430362241296</v>
       </c>
       <c r="F2">
-        <v>1353.678251672859</v>
+        <v>228.9332290733108</v>
       </c>
       <c r="G2">
         <v>31079.14188934889</v>
@@ -438,19 +438,19 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>1513.512198716085</v>
+        <v>1869.11563755113</v>
       </c>
       <c r="C3">
-        <v>1390.053734924271</v>
+        <v>1697.829556631015</v>
       </c>
       <c r="D3">
-        <v>12.12017579311776</v>
+        <v>32.68287630149236</v>
       </c>
       <c r="E3">
-        <v>1234.535389379387</v>
+        <v>2233.11278781074</v>
       </c>
       <c r="F3">
-        <v>422.4817580775864</v>
+        <v>132.5491322124458</v>
       </c>
       <c r="G3">
         <v>28034.44916393354</v>
@@ -461,19 +461,19 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>1339.915588010944</v>
+        <v>1441.375185837561</v>
       </c>
       <c r="C4">
-        <v>2924.042064732495</v>
+        <v>1828.602963157943</v>
       </c>
       <c r="D4">
-        <v>20.05719459529767</v>
+        <v>49.50356888410434</v>
       </c>
       <c r="E4">
-        <v>1646.700904396185</v>
+        <v>1758.883308686225</v>
       </c>
       <c r="F4">
-        <v>700.9609017771467</v>
+        <v>90.18586013200851</v>
       </c>
       <c r="G4">
         <v>1950.307677832142</v>
@@ -484,19 +484,19 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>921.1918622629997</v>
+        <v>157.1359851774778</v>
       </c>
       <c r="C5">
-        <v>781.6681210452316</v>
+        <v>130.8949726264793</v>
       </c>
       <c r="D5">
-        <v>6.536304608046691</v>
+        <v>2.044907846091662</v>
       </c>
       <c r="E5">
-        <v>531.0508450829358</v>
+        <v>103.6418657443282</v>
       </c>
       <c r="F5">
-        <v>230.2355918181278</v>
+        <v>6.198236728855719</v>
       </c>
       <c r="G5">
         <v>1094.385047583204</v>
@@ -507,7 +507,7 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>12.7</v>
+        <v>12.5221119865</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -553,7 +553,7 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>606.2380000000001</v>
+        <v>627.294307534464</v>
       </c>
       <c r="C8">
         <v>27.5319</v>

--- a/data/gold/results/scenarios/health_only/table_1.xlsx
+++ b/data/gold/results/scenarios/health_only/table_1.xlsx
@@ -418,13 +418,13 @@
         <v>4119.043228087125</v>
       </c>
       <c r="C2">
-        <v>3684.859392415446</v>
+        <v>3682.962592415446</v>
       </c>
       <c r="D2">
-        <v>84.42245303168855</v>
+        <v>84.40895303168854</v>
       </c>
       <c r="E2">
-        <v>4097.430362241296</v>
+        <v>4097.307162241296</v>
       </c>
       <c r="F2">
         <v>228.9332290733108</v>
@@ -556,13 +556,13 @@
         <v>627.294307534464</v>
       </c>
       <c r="C8">
-        <v>27.5319</v>
+        <v>25.6351</v>
       </c>
       <c r="D8">
-        <v>0.1911</v>
+        <v>0.1776</v>
       </c>
       <c r="E8">
-        <v>1.7924</v>
+        <v>1.6692</v>
       </c>
       <c r="F8">
         <v>0</v>
